--- a/database/Randomized_Sheet.xlsx
+++ b/database/Randomized_Sheet.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8555D9F9-E889-46E1-A6ED-9BE14C1D9F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC311919-509F-4B32-88BD-C6E0B7852568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wall" sheetId="9" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="11" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="12" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="11" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
   <si>
     <t>Batch_ID</t>
   </si>
@@ -383,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC95614-6E6A-4C7B-BA2C-E5A87B9C195C}">
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -479,7 +480,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B67" si="0">B3+1</f>
+        <f t="shared" ref="B4:B76" si="0">B3+1</f>
         <v>3</v>
       </c>
       <c r="C4">
@@ -2208,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
@@ -2238,10 +2239,10 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -2268,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -2298,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -2328,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -2355,13 +2356,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -2385,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2399,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="B68">
-        <f t="shared" ref="B68:B86" si="1">B67+1</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C68">
@@ -2415,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2429,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="B69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C69">
@@ -2445,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2459,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="B70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C70">
@@ -2475,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2489,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="B71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="C71">
@@ -2505,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2519,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="B72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C72">
@@ -2535,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -2549,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="B73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="C73">
@@ -2565,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -2579,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="B74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C74">
@@ -2589,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2598,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -2609,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="B75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C75">
@@ -2619,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -2639,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="B76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C76">
@@ -2649,13 +2650,13 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -2669,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="B77">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B77:B88" si="1">B76+1</f>
         <v>76</v>
       </c>
       <c r="C77">
@@ -2679,13 +2680,13 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -2709,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -2739,13 +2740,13 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -2769,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -2805,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -2835,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -2859,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2889,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2919,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -2949,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2961,6 +2962,66 @@
         <v>0</v>
       </c>
       <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>5</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>6</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
         <v>0</v>
       </c>
     </row>
@@ -2970,6 +3031,2594 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115A2A4A-1080-492B-AB55-548D9E7DF29C}">
+  <dimension ref="A1:I86"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>B2+1</f>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B67" si="0">B3+1</f>
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>9</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>14</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>15</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>16</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>17</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>18</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>19</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>20</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>21</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>22</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>23</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>24</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68:B86" si="1">B67+1</f>
+        <v>67</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>6</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>7</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>8</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>5</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>6</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>7</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBAB793-F06F-4A6E-9F51-E9DF2035515C}">
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4690,7 +7339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67337C74-AB80-4D81-80E2-56722238C230}">
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/database/Randomized_Sheet.xlsx
+++ b/database/Randomized_Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC311919-509F-4B32-88BD-C6E0B7852568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31CFE10F-3BF0-4E30-A8C9-71C1AC1AA794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="11">
   <si>
     <t>Batch_ID</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>GlazingR</t>
+  </si>
+  <si>
+    <t>COP</t>
   </si>
 </sst>
 </file>
@@ -384,10 +387,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC95614-6E6A-4C7B-BA2C-E5A87B9C195C}">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,8 +418,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -444,8 +450,11 @@
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -474,8 +483,11 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -504,8 +516,11 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -534,8 +549,11 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -564,8 +582,11 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -594,8 +615,11 @@
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -624,8 +648,11 @@
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -654,8 +681,11 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -684,8 +714,11 @@
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -714,8 +747,11 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -744,8 +780,11 @@
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -774,8 +813,11 @@
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -804,8 +846,11 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -834,8 +879,11 @@
       <c r="I15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -864,8 +912,11 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -894,8 +945,11 @@
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -924,8 +978,11 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -954,8 +1011,11 @@
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -984,8 +1044,11 @@
       <c r="I20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1014,8 +1077,11 @@
       <c r="I21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1044,8 +1110,11 @@
       <c r="I22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1074,8 +1143,11 @@
       <c r="I23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
@@ -1104,8 +1176,11 @@
       <c r="I24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
@@ -1134,8 +1209,11 @@
       <c r="I25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -1164,8 +1242,11 @@
       <c r="I26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
@@ -1194,8 +1275,11 @@
       <c r="I27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1</v>
       </c>
@@ -1224,8 +1308,11 @@
       <c r="I28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1254,8 +1341,11 @@
       <c r="I29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1284,8 +1374,11 @@
       <c r="I30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1314,8 +1407,11 @@
       <c r="I31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1344,8 +1440,11 @@
       <c r="I32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
@@ -1374,8 +1473,11 @@
       <c r="I33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -1404,8 +1506,11 @@
       <c r="I34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1</v>
       </c>
@@ -1434,8 +1539,11 @@
       <c r="I35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1</v>
       </c>
@@ -1464,8 +1572,11 @@
       <c r="I36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1</v>
       </c>
@@ -1494,8 +1605,11 @@
       <c r="I37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -1524,8 +1638,11 @@
       <c r="I38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1</v>
       </c>
@@ -1554,8 +1671,11 @@
       <c r="I39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1584,8 +1704,11 @@
       <c r="I40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1</v>
       </c>
@@ -1614,8 +1737,11 @@
       <c r="I41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1644,8 +1770,11 @@
       <c r="I42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1</v>
       </c>
@@ -1674,8 +1803,11 @@
       <c r="I43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1704,8 +1836,11 @@
       <c r="I44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1734,8 +1869,11 @@
       <c r="I45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -1764,8 +1902,11 @@
       <c r="I46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1794,8 +1935,11 @@
       <c r="I47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1</v>
       </c>
@@ -1824,8 +1968,11 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1</v>
       </c>
@@ -1854,8 +2001,11 @@
       <c r="I49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -1884,8 +2034,11 @@
       <c r="I50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1</v>
       </c>
@@ -1914,8 +2067,11 @@
       <c r="I51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1</v>
       </c>
@@ -1944,8 +2100,11 @@
       <c r="I52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -1974,8 +2133,11 @@
       <c r="I53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1</v>
       </c>
@@ -2004,8 +2166,11 @@
       <c r="I54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1</v>
       </c>
@@ -2034,8 +2199,11 @@
       <c r="I55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1</v>
       </c>
@@ -2064,8 +2232,11 @@
       <c r="I56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1</v>
       </c>
@@ -2094,8 +2265,11 @@
       <c r="I57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1</v>
       </c>
@@ -2124,8 +2298,11 @@
       <c r="I58">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1</v>
       </c>
@@ -2154,8 +2331,11 @@
       <c r="I59">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1</v>
       </c>
@@ -2184,8 +2364,11 @@
       <c r="I60">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1</v>
       </c>
@@ -2214,8 +2397,11 @@
       <c r="I61">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -2244,8 +2430,11 @@
       <c r="I62">
         <v>7</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1</v>
       </c>
@@ -2274,8 +2463,11 @@
       <c r="I63">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
@@ -2304,8 +2496,11 @@
       <c r="I64">
         <v>9</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1</v>
       </c>
@@ -2334,8 +2529,11 @@
       <c r="I65">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1</v>
       </c>
@@ -2364,8 +2562,11 @@
       <c r="I66">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1</v>
       </c>
@@ -2394,8 +2595,11 @@
       <c r="I67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1</v>
       </c>
@@ -2424,8 +2628,11 @@
       <c r="I68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1</v>
       </c>
@@ -2454,8 +2661,11 @@
       <c r="I69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1</v>
       </c>
@@ -2484,8 +2694,11 @@
       <c r="I70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1</v>
       </c>
@@ -2514,8 +2727,11 @@
       <c r="I71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1</v>
       </c>
@@ -2544,8 +2760,11 @@
       <c r="I72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1</v>
       </c>
@@ -2574,8 +2793,11 @@
       <c r="I73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1</v>
       </c>
@@ -2604,8 +2826,11 @@
       <c r="I74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1</v>
       </c>
@@ -2634,8 +2859,11 @@
       <c r="I75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1</v>
       </c>
@@ -2664,13 +2892,16 @@
       <c r="I76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77">
-        <f t="shared" ref="B77:B88" si="1">B76+1</f>
+        <f t="shared" ref="B77:B92" si="1">B76+1</f>
         <v>76</v>
       </c>
       <c r="C77">
@@ -2694,8 +2925,11 @@
       <c r="I77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1</v>
       </c>
@@ -2724,8 +2958,11 @@
       <c r="I78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1</v>
       </c>
@@ -2754,8 +2991,11 @@
       <c r="I79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1</v>
       </c>
@@ -2784,8 +3024,11 @@
       <c r="I80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1</v>
       </c>
@@ -2814,8 +3057,11 @@
       <c r="I81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1</v>
       </c>
@@ -2844,8 +3090,11 @@
       <c r="I82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1</v>
       </c>
@@ -2874,8 +3123,11 @@
       <c r="I83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1</v>
       </c>
@@ -2904,8 +3156,11 @@
       <c r="I84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1</v>
       </c>
@@ -2934,8 +3189,11 @@
       <c r="I85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -2964,8 +3222,11 @@
       <c r="I86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1</v>
       </c>
@@ -2994,8 +3255,11 @@
       <c r="I87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1</v>
       </c>
@@ -3023,6 +3287,141 @@
       </c>
       <c r="I88">
         <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
